--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N12_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.85035215423063</v>
+        <v>7.288182225062477</v>
       </c>
       <c r="D2" t="n">
-        <v>29.49958294754691</v>
+        <v>4.793682228976373</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
